--- a/src/results/(Terstruktur)Data Scrapping.xlsx
+++ b/src/results/(Terstruktur)Data Scrapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pekerjaan\Dashboard-Pertamina-VeloCT\src\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21373F35-CC67-4124-87FC-4D9D0D5BE492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F71413-6B69-4C1F-9003-C492BE1928B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(Data)Biodesel" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="376">
   <si>
     <t>Date</t>
   </si>
@@ -897,9 +897,6 @@
   </si>
   <si>
     <t>Harga Tetes Tebu</t>
-  </si>
-  <si>
-    <t>2023-11-29</t>
   </si>
   <si>
     <t>2025-08-29</t>
@@ -1162,8 +1159,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1240,15 +1237,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1555,9 +1555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C144"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>10143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>8794</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>8939</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>9343</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>9112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>8954</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>8922</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>8770</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>7829</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>7494</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>6478</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>9456</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>9271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9081</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>7680</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>6686</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>6890</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>7039</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>6626</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>6954</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>7112</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>7687</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>8026</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>8891</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>8737</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>8402</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>7835</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>8483</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>9028</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>8262</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>8779</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>9362</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>9493</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>9358</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>8815</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>8230</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>8302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>7965</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>8518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>8490</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>8491</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>7962</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>8161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>8356</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>8261</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>8140</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>7949</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>7341</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>7227</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>7015</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>7403</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>7387</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>7348</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>6977</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>6970</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>7358</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>8706</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>9539</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>8933</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>8019</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>7321</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>7887</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>9003</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>9265</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9329</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>9457</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>9579</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>9434</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>10131</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>179</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>10229</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>11034</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>9852</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>10635</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>11930</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>189</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>12022</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>12854</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>13746</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>13177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>13867</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>14436</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>15559</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>15211</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>205</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>13033</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>207</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>11070</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>209</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>8047</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>10281</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>10787</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>11012</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>12039</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>219</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>11233</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>223</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>11473</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>12262</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>11493</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>10235</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>9998</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>10620</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>10687</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>10670</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>10653</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>10974</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>11371</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>11517</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>12178</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>12453</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>11732</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>12161</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>12382</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>12389</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>12633</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>13384</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>14389</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>14615</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>13231</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>13929</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>14290</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>13742</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>12890</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>12874</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>13527</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>13948</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>14036</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -3148,1373 +3148,1360 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C2">
-        <v>13725</v>
+        <v>13436</v>
       </c>
       <c r="D2">
-        <v>2378</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C3">
-        <v>13436</v>
+        <v>13508</v>
       </c>
       <c r="D3">
         <v>2294</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C4">
-        <v>13508</v>
+        <v>13423</v>
       </c>
       <c r="D4">
-        <v>2294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C5">
-        <v>13423</v>
+        <v>13432</v>
       </c>
       <c r="D5">
         <v>2264</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C6">
-        <v>13432</v>
+        <v>13385</v>
       </c>
       <c r="D6">
-        <v>2264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C7">
-        <v>13385</v>
+        <v>13356</v>
       </c>
       <c r="D7">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C8">
-        <v>13356</v>
+        <v>10832</v>
       </c>
       <c r="D8">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C9">
-        <v>10832</v>
+        <v>10538</v>
       </c>
       <c r="D9">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C10">
-        <v>10538</v>
+        <v>9613</v>
       </c>
       <c r="D10">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C11">
-        <v>9613</v>
+        <v>9263</v>
       </c>
       <c r="D11">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C12">
-        <v>9263</v>
+        <v>9013</v>
       </c>
       <c r="D12">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C13">
-        <v>9013</v>
+        <v>8428</v>
       </c>
       <c r="D13">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B14" t="s">
-        <v>288</v>
-      </c>
-      <c r="C14">
-        <v>8428</v>
-      </c>
-      <c r="D14">
         <v>1034</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D83"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2">
         <v>56.55</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2019</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C3">
         <v>61.31</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C4">
         <v>63.6</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2019</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C5">
         <v>68.31</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2019</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C6">
         <v>68.069999999999993</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7">
         <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2019</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C8">
         <v>61.32</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C9">
         <v>57.27</v>
       </c>
       <c r="D9" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C10">
         <v>60.84</v>
       </c>
       <c r="D10" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C11">
         <v>59.82</v>
       </c>
       <c r="D11" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2019</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C12">
         <v>63.26</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2019</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C13">
         <v>67.180000000000007</v>
       </c>
       <c r="D13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2020</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C14">
         <v>65.38</v>
       </c>
       <c r="D14" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2020</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C15">
         <v>56.61</v>
       </c>
       <c r="D15" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2020</v>
       </c>
       <c r="B16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C16">
         <v>34.229999999999997</v>
       </c>
       <c r="D16" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2020</v>
       </c>
       <c r="B17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C17">
         <v>20.66</v>
       </c>
       <c r="D17" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2020</v>
       </c>
       <c r="B18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C18">
         <v>25.67</v>
       </c>
       <c r="D18" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2020</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C19">
         <v>36.68</v>
       </c>
       <c r="D19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2020</v>
       </c>
       <c r="B20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C20">
         <v>40.64</v>
       </c>
       <c r="D20" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2020</v>
       </c>
       <c r="B21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C21">
         <v>41.63</v>
       </c>
       <c r="D21" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2020</v>
       </c>
       <c r="B22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C22">
         <v>37.43</v>
       </c>
       <c r="D22" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2020</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C23">
         <v>38.07</v>
       </c>
       <c r="D23" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2020</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C24">
         <v>40.67</v>
       </c>
       <c r="D24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2020</v>
       </c>
       <c r="B25" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C25">
         <v>47.78</v>
       </c>
       <c r="D25" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2021</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C26">
         <v>53.17</v>
       </c>
       <c r="D26" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2021</v>
       </c>
       <c r="B27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C27">
         <v>60.36</v>
       </c>
       <c r="D27" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2021</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C28">
         <v>63.5</v>
       </c>
       <c r="D28" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2021</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C29">
         <v>61.96</v>
       </c>
       <c r="D29" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2021</v>
       </c>
       <c r="B30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30">
         <v>65.489999999999995</v>
       </c>
       <c r="D30" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2021</v>
       </c>
       <c r="B31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31">
         <v>70.23</v>
       </c>
       <c r="D31" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32">
         <v>72.17</v>
       </c>
       <c r="D32" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C33">
         <v>67.8</v>
       </c>
       <c r="D33" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C34">
         <v>72.2</v>
       </c>
       <c r="D34" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>2021</v>
       </c>
       <c r="B35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C35">
         <v>81.8</v>
       </c>
       <c r="D35" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>2021</v>
       </c>
       <c r="B36" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C36">
         <v>80.13</v>
       </c>
       <c r="D36" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>2021</v>
       </c>
       <c r="B37" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C37">
         <v>73.36</v>
       </c>
       <c r="D37" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>2022</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C38">
         <v>85.89</v>
       </c>
       <c r="D38" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2022</v>
       </c>
       <c r="B39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C39">
         <v>95.72</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>2022</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40">
         <v>113.5</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2022</v>
       </c>
       <c r="B41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C41">
         <v>102.51</v>
       </c>
       <c r="D41" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>2022</v>
       </c>
       <c r="B42" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42">
         <v>109.61</v>
       </c>
       <c r="D42" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>2022</v>
       </c>
       <c r="B43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C43">
         <v>117.62</v>
       </c>
       <c r="D43" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>2022</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C44">
         <v>106.73</v>
       </c>
       <c r="D44" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>2022</v>
       </c>
       <c r="B45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C45">
         <v>94.17</v>
       </c>
       <c r="D45" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>2022</v>
       </c>
       <c r="B46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C46">
         <v>86.07</v>
       </c>
       <c r="D46" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>2022</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C47">
         <v>89.1</v>
       </c>
       <c r="D47" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2022</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48">
         <v>87.5</v>
       </c>
       <c r="D48" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>2022</v>
       </c>
       <c r="B49" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C49">
         <v>76.66</v>
       </c>
       <c r="D49" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>2023</v>
       </c>
       <c r="B50" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C50">
         <v>78.540000000000006</v>
       </c>
       <c r="D50" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2023</v>
       </c>
       <c r="B51" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C51">
         <v>79.48</v>
       </c>
       <c r="D51" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>2023</v>
       </c>
       <c r="B52" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C52">
         <v>74.59</v>
       </c>
       <c r="D52" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>2023</v>
       </c>
       <c r="B53" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C53">
         <v>79.34</v>
       </c>
       <c r="D53" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>2023</v>
       </c>
       <c r="B54" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C54">
         <v>70.12</v>
       </c>
       <c r="D54" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>2023</v>
       </c>
       <c r="B55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C55">
         <v>69.36</v>
       </c>
       <c r="D55" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2023</v>
       </c>
       <c r="B56" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2023</v>
       </c>
       <c r="B57" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C57">
         <v>82.59</v>
       </c>
       <c r="D57" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2023</v>
       </c>
       <c r="B58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C58">
         <v>90.17</v>
       </c>
       <c r="D58" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2023</v>
       </c>
       <c r="B59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C59">
         <v>86.72</v>
       </c>
       <c r="D59" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2023</v>
       </c>
       <c r="B60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C60">
         <v>79.63</v>
       </c>
       <c r="D60" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2023</v>
       </c>
       <c r="B61" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C61">
         <v>75.510000000000005</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2024</v>
       </c>
       <c r="B62" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C62">
         <v>77.12</v>
       </c>
       <c r="D62" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2024</v>
       </c>
       <c r="B63" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C63">
         <v>80.09</v>
       </c>
       <c r="D63" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2024</v>
       </c>
       <c r="B64" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C64">
         <v>83.78</v>
       </c>
       <c r="D64" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2024</v>
       </c>
       <c r="B65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C65">
         <v>87.61</v>
       </c>
       <c r="D65" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2024</v>
       </c>
       <c r="B66" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C66">
         <v>79.78</v>
       </c>
       <c r="D66" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2024</v>
       </c>
       <c r="B67" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C67">
         <v>79.31</v>
       </c>
       <c r="D67" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2024</v>
       </c>
       <c r="B68" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C68">
         <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2024</v>
       </c>
       <c r="B69" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C69">
         <v>78.510000000000005</v>
       </c>
       <c r="D69" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2024</v>
       </c>
       <c r="B70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C70">
         <v>72.540000000000006</v>
       </c>
       <c r="D70" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2024</v>
       </c>
       <c r="B71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C71">
         <v>73.53</v>
       </c>
       <c r="D71" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2024</v>
       </c>
       <c r="B72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C72">
         <v>71.83</v>
       </c>
       <c r="D72" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2024</v>
       </c>
       <c r="B73" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C73">
         <v>71.61</v>
       </c>
       <c r="D73" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2025</v>
       </c>
       <c r="B74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C74" t="s">
+        <v>353</v>
+      </c>
+      <c r="D74" t="s">
         <v>354</v>
       </c>
-      <c r="D74" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2025</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C75" t="s">
+        <v>355</v>
+      </c>
+      <c r="D75" t="s">
         <v>356</v>
       </c>
-      <c r="D75" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2025</v>
       </c>
       <c r="B76" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76">
         <v>71.11</v>
       </c>
       <c r="D76" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>2025</v>
       </c>
       <c r="B77" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C77">
         <v>65.290000000000006</v>
       </c>
       <c r="D77" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C78">
         <v>62.75</v>
       </c>
       <c r="D78" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>2025</v>
       </c>
       <c r="B79" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C79">
         <v>69.33</v>
       </c>
       <c r="D79" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>2025</v>
       </c>
       <c r="B80" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80">
         <v>68.59</v>
       </c>
       <c r="D80" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>2025</v>
       </c>
       <c r="B81" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C81">
         <v>66.069999999999993</v>
       </c>
       <c r="D81" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>2025</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C82">
         <v>66.81</v>
       </c>
       <c r="D82" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>2025</v>
       </c>
       <c r="B83" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C83" t="s">
+        <v>363</v>
+      </c>
+      <c r="D83" t="s">
         <v>364</v>
-      </c>
-      <c r="D83" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -4525,43 +4512,43 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B2">
         <v>2015</v>
@@ -4591,9 +4578,9 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B3">
         <v>2015</v>
@@ -4623,9 +4610,9 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B4">
         <v>2015</v>
@@ -4655,9 +4642,9 @@
         <v>47.92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B5">
         <v>2015</v>
@@ -4687,9 +4674,9 @@
         <v>50.79</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B6">
         <v>2015</v>
@@ -4719,9 +4706,9 @@
         <v>50.06</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B7">
         <v>2015</v>
@@ -4751,9 +4738,9 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B8">
         <v>2015</v>
@@ -4783,9 +4770,9 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B9">
         <v>2015</v>
@@ -4815,9 +4802,9 @@
         <v>48.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10">
         <v>2015</v>
@@ -4847,9 +4834,9 @@
         <v>48.84</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B11">
         <v>2015</v>
@@ -4879,9 +4866,9 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B12">
         <v>2016</v>
@@ -4911,9 +4898,9 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B13">
         <v>2016</v>
@@ -4943,9 +4930,9 @@
         <v>50.38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B14">
         <v>2016</v>
@@ -4975,9 +4962,9 @@
         <v>50.01</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B15">
         <v>2016</v>
@@ -5007,9 +4994,9 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B16">
         <v>2016</v>
@@ -5039,9 +5026,9 @@
         <v>50.62</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B17">
         <v>2016</v>
@@ -5071,9 +5058,9 @@
         <v>50.32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B18">
         <v>2016</v>
@@ -5103,9 +5090,9 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B19">
         <v>2016</v>
@@ -5135,9 +5122,9 @@
         <v>51.24</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B20">
         <v>2016</v>
@@ -5167,9 +5154,9 @@
         <v>49.94</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B21">
         <v>2016</v>
@@ -5199,9 +5186,9 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B22">
         <v>2016</v>
@@ -5231,9 +5218,9 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B23">
         <v>2016</v>
@@ -5263,9 +5250,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B24">
         <v>2017</v>
@@ -5295,9 +5282,9 @@
         <v>49.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B25">
         <v>2017</v>
@@ -5327,9 +5314,9 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B26">
         <v>2017</v>
@@ -5359,9 +5346,9 @@
         <v>51.71</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B27">
         <v>2017</v>
@@ -5391,9 +5378,9 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B28">
         <v>2017</v>
@@ -5423,9 +5410,9 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B29">
         <v>2017</v>
@@ -5455,9 +5442,9 @@
         <v>53.34</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B30">
         <v>2017</v>
@@ -5487,9 +5474,9 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B31">
         <v>2017</v>
@@ -5519,9 +5506,9 @@
         <v>51.76</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32">
         <v>2017</v>
@@ -5551,9 +5538,9 @@
         <v>53.05</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B33">
         <v>2017</v>
@@ -5583,9 +5570,9 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B34">
         <v>2017</v>
@@ -5615,9 +5602,9 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B35">
         <v>2017</v>
@@ -5647,9 +5634,9 @@
         <v>51.65</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B36">
         <v>2018</v>
@@ -5679,9 +5666,9 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B37">
         <v>2018</v>
@@ -5711,9 +5698,9 @@
         <v>51.44</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B38">
         <v>2018</v>
@@ -5743,9 +5730,9 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B39">
         <v>2018</v>
@@ -5775,9 +5762,9 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B40">
         <v>2018</v>
@@ -5807,9 +5794,9 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B41">
         <v>2018</v>
@@ -5839,9 +5826,9 @@
         <v>52.92</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B42">
         <v>2018</v>
@@ -5871,9 +5858,9 @@
         <v>52.68</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B43">
         <v>2018</v>
@@ -5903,9 +5890,9 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B44">
         <v>2018</v>
@@ -5935,9 +5922,9 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B45">
         <v>2018</v>
@@ -5967,9 +5954,9 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B46">
         <v>2018</v>
@@ -5999,9 +5986,9 @@
         <v>52.33</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B47">
         <v>2018</v>
@@ -6031,9 +6018,9 @@
         <v>53.01</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B48">
         <v>2019</v>
@@ -6063,9 +6050,9 @@
         <v>51.36</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B49">
         <v>2019</v>
@@ -6095,9 +6082,9 @@
         <v>52.02</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B50">
         <v>2019</v>
@@ -6127,9 +6114,9 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B51">
         <v>2019</v>
@@ -6159,9 +6146,9 @@
         <v>52.61</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B52">
         <v>2019</v>
@@ -6191,9 +6178,9 @@
         <v>53.23</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B53">
         <v>2019</v>
@@ -6223,9 +6210,9 @@
         <v>53.51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B54">
         <v>2019</v>
@@ -6255,9 +6242,9 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B55">
         <v>2019</v>
@@ -6287,9 +6274,9 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B56">
         <v>2019</v>
@@ -6319,9 +6306,9 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B57">
         <v>2019</v>
@@ -6351,9 +6338,9 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B58">
         <v>2019</v>
@@ -6383,9 +6370,9 @@
         <v>53.19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B59">
         <v>2019</v>
@@ -6415,9 +6402,9 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B60">
         <v>2020</v>
@@ -6447,9 +6434,9 @@
         <v>47.69</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B61">
         <v>2020</v>
@@ -6479,9 +6466,9 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B62">
         <v>2020</v>
@@ -6511,9 +6498,9 @@
         <v>47.63</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B63">
         <v>2020</v>
@@ -6543,9 +6530,9 @@
         <v>48.26</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B64">
         <v>2020</v>
@@ -6575,9 +6562,9 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B65">
         <v>2020</v>
@@ -6607,9 +6594,9 @@
         <v>49.34</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B66">
         <v>2020</v>
@@ -6639,9 +6626,9 @@
         <v>49.54</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B67">
         <v>2020</v>
@@ -6671,9 +6658,9 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B68">
         <v>2020</v>
@@ -6703,9 +6690,9 @@
         <v>50.15</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69">
         <v>2020</v>
@@ -6735,9 +6722,9 @@
         <v>49.18</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B70">
         <v>2020</v>
@@ -6767,9 +6754,9 @@
         <v>49.89</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B71">
         <v>2020</v>
@@ -6799,9 +6786,9 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B72">
         <v>2021</v>
@@ -6831,9 +6818,9 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B73">
         <v>2021</v>
@@ -6863,9 +6850,9 @@
         <v>51.74</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B74">
         <v>2021</v>
@@ -6895,9 +6882,9 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B75">
         <v>2021</v>
@@ -6927,9 +6914,9 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B76">
         <v>2021</v>
@@ -6959,9 +6946,9 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B77">
         <v>2021</v>
@@ -6991,9 +6978,9 @@
         <v>52.86</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B78">
         <v>2021</v>
@@ -7023,9 +7010,9 @@
         <v>52.47</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B79">
         <v>2021</v>
@@ -7055,9 +7042,9 @@
         <v>52.14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B80">
         <v>2021</v>
@@ -7087,9 +7074,9 @@
         <v>52.76</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B81">
         <v>2021</v>
@@ -7119,9 +7106,9 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B82">
         <v>2021</v>
@@ -7151,9 +7138,9 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B83">
         <v>2021</v>
@@ -7183,9 +7170,9 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B84">
         <v>2022</v>
@@ -7215,9 +7202,9 @@
         <v>52.69</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B85">
         <v>2022</v>
@@ -7247,9 +7234,9 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B86">
         <v>2022</v>
@@ -7279,9 +7266,9 @@
         <v>53.02</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B87">
         <v>2022</v>
@@ -7311,9 +7298,9 @@
         <v>53.36</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B88">
         <v>2022</v>
@@ -7343,9 +7330,9 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B89">
         <v>2022</v>
@@ -7375,9 +7362,9 @@
         <v>54.79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B90">
         <v>2022</v>
@@ -7407,9 +7394,9 @@
         <v>54.42</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B91">
         <v>2022</v>
@@ -7439,9 +7426,9 @@
         <v>54.16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B92">
         <v>2022</v>
@@ -7471,9 +7458,9 @@
         <v>54.83</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B93">
         <v>2022</v>
@@ -7503,9 +7490,9 @@
         <v>53.72</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B94">
         <v>2022</v>
@@ -7535,9 +7522,9 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B95">
         <v>2022</v>
@@ -7567,9 +7554,9 @@
         <v>54.92</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B96">
         <v>2023</v>
@@ -7599,9 +7586,9 @@
         <v>54.54</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B97">
         <v>2023</v>
@@ -7631,9 +7618,9 @@
         <v>55.95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B98">
         <v>2023</v>
@@ -7663,9 +7650,9 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B99">
         <v>2023</v>
@@ -7695,9 +7682,9 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B100">
         <v>2023</v>
@@ -7727,9 +7714,9 @@
         <v>56.58</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B101">
         <v>2023</v>
@@ -7759,9 +7746,9 @@
         <v>57.11</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B102">
         <v>2023</v>
@@ -7791,9 +7778,9 @@
         <v>56.68</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B103">
         <v>2023</v>
@@ -7823,9 +7810,9 @@
         <v>56.31</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B104">
         <v>2023</v>
@@ -7855,9 +7842,9 @@
         <v>56.97</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B105">
         <v>2023</v>
@@ -7887,9 +7874,9 @@
         <v>55.84</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B106">
         <v>2023</v>
@@ -7919,9 +7906,9 @@
         <v>56.61</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B107">
         <v>2023</v>
@@ -7951,9 +7938,9 @@
         <v>57.23</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B108">
         <v>2024</v>
@@ -7983,9 +7970,9 @@
         <v>56.38</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B109">
         <v>2024</v>
@@ -8015,9 +8002,9 @@
         <v>57.81</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B110">
         <v>2024</v>
@@ -8047,9 +8034,9 @@
         <v>57.07</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B111">
         <v>2024</v>
@@ -8079,9 +8066,9 @@
         <v>56.86</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B112">
         <v>2024</v>
@@ -8111,9 +8098,9 @@
         <v>57.24</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B113">
         <v>2024</v>
@@ -8143,9 +8130,9 @@
         <v>57.89</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B114">
         <v>2024</v>
@@ -8175,9 +8162,9 @@
         <v>57.48</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B115">
         <v>2024</v>
@@ -8207,9 +8194,9 @@
         <v>56.77</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B116">
         <v>2024</v>
@@ -8239,9 +8226,9 @@
         <v>57.38</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B117">
         <v>2024</v>
@@ -8271,9 +8258,9 @@
         <v>56.28</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B118">
         <v>2024</v>
@@ -8303,9 +8290,9 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B119">
         <v>2024</v>
@@ -8335,9 +8322,9 @@
         <v>58.28</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B120">
         <v>2025</v>
@@ -8367,9 +8354,9 @@
         <v>56.88</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B121">
         <v>2025</v>
@@ -8399,9 +8386,9 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B122">
         <v>2025</v>
@@ -8431,9 +8418,9 @@
         <v>57.49</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B123">
         <v>2025</v>
@@ -8463,9 +8450,9 @@
         <v>57.88</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B124">
         <v>2025</v>
@@ -8495,9 +8482,9 @@
         <v>58.54</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B125">
         <v>2025</v>
@@ -8527,9 +8514,9 @@
         <v>59.18</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B126">
         <v>2025</v>
@@ -8559,9 +8546,9 @@
         <v>58.65</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B127">
         <v>2025</v>
@@ -8591,9 +8578,9 @@
         <v>58.25</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B128">
         <v>2025</v>
@@ -8623,9 +8610,9 @@
         <v>59.04</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B129">
         <v>2025</v>
@@ -8655,9 +8642,9 @@
         <v>57.92</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B130">
         <v>2025</v>
@@ -8695,20 +8682,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C339"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45958</v>
       </c>
@@ -8719,7 +8706,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45958</v>
       </c>
@@ -8730,7 +8717,7 @@
         <v>13185</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45958</v>
       </c>
@@ -8741,7 +8728,7 @@
         <v>13170</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45958</v>
       </c>
@@ -8752,7 +8739,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45958</v>
       </c>
@@ -8763,7 +8750,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45958</v>
       </c>
@@ -8774,7 +8761,7 @@
         <v>13175</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45958</v>
       </c>
@@ -8785,7 +8772,7 @@
         <v>12888</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45958</v>
       </c>
@@ -8796,7 +8783,7 @@
         <v>12638</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45958</v>
       </c>
@@ -8807,7 +8794,7 @@
         <v>12718</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45958</v>
       </c>
@@ -8818,7 +8805,7 @@
         <v>12729</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45958</v>
       </c>
@@ -8829,7 +8816,7 @@
         <v>12640</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45958</v>
       </c>
@@ -8840,7 +8827,7 @@
         <v>12723</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45958</v>
       </c>
@@ -8851,7 +8838,7 @@
         <v>12738</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -8862,7 +8849,7 @@
         <v>12740</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45958</v>
       </c>
@@ -8873,7 +8860,7 @@
         <v>12725</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45958</v>
       </c>
@@ -8884,7 +8871,7 @@
         <v>12810</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45958</v>
       </c>
@@ -8895,7 +8882,7 @@
         <v>12804</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45958</v>
       </c>
@@ -8906,7 +8893,7 @@
         <v>12757</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45958</v>
       </c>
@@ -8917,7 +8904,7 @@
         <v>12775</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45958</v>
       </c>
@@ -8928,7 +8915,7 @@
         <v>12965</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45958</v>
       </c>
@@ -8939,7 +8926,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45958</v>
       </c>
@@ -8950,7 +8937,7 @@
         <v>13050</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45958</v>
       </c>
@@ -8961,7 +8948,7 @@
         <v>13036</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45958</v>
       </c>
@@ -8972,7 +8959,7 @@
         <v>13040</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45958</v>
       </c>
@@ -8983,7 +8970,7 @@
         <v>13105</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>45958</v>
       </c>
@@ -8994,7 +8981,7 @@
         <v>13209</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>45958</v>
       </c>
@@ -9005,7 +8992,7 @@
         <v>13119</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45958</v>
       </c>
@@ -9016,7 +9003,7 @@
         <v>13054</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45958</v>
       </c>
@@ -9027,7 +9014,7 @@
         <v>12939</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45958</v>
       </c>
@@ -9038,7 +9025,7 @@
         <v>12918</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45958</v>
       </c>
@@ -9049,7 +9036,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45958</v>
       </c>
@@ -9060,7 +9047,7 @@
         <v>12782</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45958</v>
       </c>
@@ -9071,7 +9058,7 @@
         <v>12677</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45958</v>
       </c>
@@ -9082,7 +9069,7 @@
         <v>12520</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45958</v>
       </c>
@@ -9093,7 +9080,7 @@
         <v>12588</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45958</v>
       </c>
@@ -9104,7 +9091,7 @@
         <v>12625</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45958</v>
       </c>
@@ -9115,7 +9102,7 @@
         <v>12675</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45958</v>
       </c>
@@ -9126,7 +9113,7 @@
         <v>12745</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45958</v>
       </c>
@@ -9137,7 +9124,7 @@
         <v>12868</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45958</v>
       </c>
@@ -9148,7 +9135,7 @@
         <v>12959</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45958</v>
       </c>
@@ -9159,7 +9146,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45958</v>
       </c>
@@ -9170,7 +9157,7 @@
         <v>13233</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45958</v>
       </c>
@@ -9181,7 +9168,7 @@
         <v>13235</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45958</v>
       </c>
@@ -9192,7 +9179,7 @@
         <v>13155</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45958</v>
       </c>
@@ -9203,7 +9190,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45958</v>
       </c>
@@ -9214,7 +9201,7 @@
         <v>13242</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45958</v>
       </c>
@@ -9225,7 +9212,7 @@
         <v>13342</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45958</v>
       </c>
@@ -9236,7 +9223,7 @@
         <v>13212</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45958</v>
       </c>
@@ -9247,7 +9234,7 @@
         <v>13131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45958</v>
       </c>
@@ -9258,7 +9245,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45958</v>
       </c>
@@ -9269,7 +9256,7 @@
         <v>13058</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45958</v>
       </c>
@@ -9280,7 +9267,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>45958</v>
       </c>
@@ -9291,7 +9278,7 @@
         <v>13118</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>45958</v>
       </c>
@@ -9302,7 +9289,7 @@
         <v>13070</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>45958</v>
       </c>
@@ -9313,7 +9300,7 @@
         <v>13035</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>45958</v>
       </c>
@@ -9324,7 +9311,7 @@
         <v>12925</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45958</v>
       </c>
@@ -9335,7 +9322,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45958</v>
       </c>
@@ -9346,7 +9333,7 @@
         <v>13358</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45958</v>
       </c>
@@ -9357,7 +9344,7 @@
         <v>13407</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45958</v>
       </c>
@@ -9368,7 +9355,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45958</v>
       </c>
@@ -9379,7 +9366,7 @@
         <v>13570</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45958</v>
       </c>
@@ -9390,7 +9377,7 @@
         <v>13759</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45958</v>
       </c>
@@ -9401,7 +9388,7 @@
         <v>13928</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45958</v>
       </c>
@@ -9412,7 +9399,7 @@
         <v>14004</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45958</v>
       </c>
@@ -9423,7 +9410,7 @@
         <v>13978</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45958</v>
       </c>
@@ -9434,7 +9421,7 @@
         <v>14106</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45958</v>
       </c>
@@ -9445,7 +9432,7 @@
         <v>14027</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45958</v>
       </c>
@@ -9456,7 +9443,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45958</v>
       </c>
@@ -9467,7 +9454,7 @@
         <v>14322</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45958</v>
       </c>
@@ -9478,7 +9465,7 @@
         <v>14242</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45958</v>
       </c>
@@ -9489,7 +9476,7 @@
         <v>14040</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45958</v>
       </c>
@@ -9500,7 +9487,7 @@
         <v>14078</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45958</v>
       </c>
@@ -9511,7 +9498,7 @@
         <v>14029</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45958</v>
       </c>
@@ -9522,7 +9509,7 @@
         <v>14262</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45958</v>
       </c>
@@ -9533,7 +9520,7 @@
         <v>14135</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45958</v>
       </c>
@@ -9544,7 +9531,7 @@
         <v>13977</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45958</v>
       </c>
@@ -9555,7 +9542,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45958</v>
       </c>
@@ -9566,7 +9553,7 @@
         <v>14038</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45958</v>
       </c>
@@ -9577,7 +9564,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45958</v>
       </c>
@@ -9588,7 +9575,7 @@
         <v>14020</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>45958</v>
       </c>
@@ -9599,7 +9586,7 @@
         <v>14183</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>45958</v>
       </c>
@@ -9610,7 +9597,7 @@
         <v>14337</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>45958</v>
       </c>
@@ -9621,7 +9608,7 @@
         <v>14507</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>45958</v>
       </c>
@@ -9632,7 +9619,7 @@
         <v>14721</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45958</v>
       </c>
@@ -9643,7 +9630,7 @@
         <v>14685</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45958</v>
       </c>
@@ -9654,7 +9641,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45958</v>
       </c>
@@ -9665,7 +9652,7 @@
         <v>14810</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45958</v>
       </c>
@@ -9676,7 +9663,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45958</v>
       </c>
@@ -9687,7 +9674,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45958</v>
       </c>
@@ -9698,7 +9685,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45958</v>
       </c>
@@ -9709,7 +9696,7 @@
         <v>15310</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45958</v>
       </c>
@@ -9720,7 +9707,7 @@
         <v>15330</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45958</v>
       </c>
@@ -9731,7 +9718,7 @@
         <v>15430</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45958</v>
       </c>
@@ -9742,7 +9729,7 @@
         <v>15544</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45958</v>
       </c>
@@ -9753,7 +9740,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45958</v>
       </c>
@@ -9764,7 +9751,7 @@
         <v>15738</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45958</v>
       </c>
@@ -9775,7 +9762,7 @@
         <v>15367</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45958</v>
       </c>
@@ -9786,7 +9773,7 @@
         <v>15254</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45958</v>
       </c>
@@ -9797,7 +9784,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45958</v>
       </c>
@@ -9808,7 +9795,7 @@
         <v>15255</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45958</v>
       </c>
@@ -9819,7 +9806,7 @@
         <v>15365</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45958</v>
       </c>
@@ -9830,7 +9817,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45958</v>
       </c>
@@ -9841,7 +9828,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45958</v>
       </c>
@@ -9852,7 +9839,7 @@
         <v>14813</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45958</v>
       </c>
@@ -9863,7 +9850,7 @@
         <v>14964</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45958</v>
       </c>
@@ -9874,7 +9861,7 @@
         <v>15165</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45958</v>
       </c>
@@ -9885,7 +9872,7 @@
         <v>15245</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45958</v>
       </c>
@@ -9896,7 +9883,7 @@
         <v>15584</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>45958</v>
       </c>
@@ -9907,7 +9894,7 @@
         <v>15656</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>45958</v>
       </c>
@@ -9918,7 +9905,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>45958</v>
       </c>
@@ -9929,7 +9916,7 @@
         <v>15900</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>45958</v>
       </c>
@@ -9940,7 +9927,7 @@
         <v>15976</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45958</v>
       </c>
@@ -9951,7 +9938,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45958</v>
       </c>
@@ -9962,7 +9949,7 @@
         <v>15940</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45958</v>
       </c>
@@ -9973,7 +9960,7 @@
         <v>15760</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45958</v>
       </c>
@@ -9984,7 +9971,7 @@
         <v>15675</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45958</v>
       </c>
@@ -9995,7 +9982,7 @@
         <v>15602</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45958</v>
       </c>
@@ -10006,7 +9993,7 @@
         <v>15553</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45958</v>
       </c>
@@ -10017,7 +10004,7 @@
         <v>15589</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45958</v>
       </c>
@@ -10028,7 +10015,7 @@
         <v>15327</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45958</v>
       </c>
@@ -10039,7 +10026,7 @@
         <v>14919</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45958</v>
       </c>
@@ -10050,7 +10037,7 @@
         <v>14646</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45958</v>
       </c>
@@ -10061,7 +10048,7 @@
         <v>14684</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45958</v>
       </c>
@@ -10072,7 +10059,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45958</v>
       </c>
@@ -10083,7 +10070,7 @@
         <v>14858</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45958</v>
       </c>
@@ -10094,7 +10081,7 @@
         <v>14454</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45958</v>
       </c>
@@ -10105,7 +10092,7 @@
         <v>14253</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45958</v>
       </c>
@@ -10116,7 +10103,7 @@
         <v>14157</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45958</v>
       </c>
@@ -10127,7 +10114,7 @@
         <v>14069</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45958</v>
       </c>
@@ -10138,7 +10125,7 @@
         <v>13852</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45958</v>
       </c>
@@ -10149,7 +10136,7 @@
         <v>13895</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45958</v>
       </c>
@@ -10160,7 +10147,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45958</v>
       </c>
@@ -10171,7 +10158,7 @@
         <v>14188</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45958</v>
       </c>
@@ -10182,7 +10169,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45958</v>
       </c>
@@ -10193,7 +10180,7 @@
         <v>13712</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45958</v>
       </c>
@@ -10204,7 +10191,7 @@
         <v>13585</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>45958</v>
       </c>
@@ -10215,7 +10202,7 @@
         <v>13725</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>45958</v>
       </c>
@@ -10226,7 +10213,7 @@
         <v>13816</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>45958</v>
       </c>
@@ -10237,7 +10224,7 @@
         <v>13670</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>45958</v>
       </c>
@@ -10248,7 +10235,7 @@
         <v>13533</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45958</v>
       </c>
@@ -10259,7 +10246,7 @@
         <v>13605</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45958</v>
       </c>
@@ -10270,7 +10257,7 @@
         <v>13750</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45958</v>
       </c>
@@ -10281,7 +10268,7 @@
         <v>13889</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45958</v>
       </c>
@@ -10292,7 +10279,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45958</v>
       </c>
@@ -10303,7 +10290,7 @@
         <v>14008</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45958</v>
       </c>
@@ -10314,7 +10301,7 @@
         <v>14150</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45958</v>
       </c>
@@ -10325,7 +10312,7 @@
         <v>14265</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45958</v>
       </c>
@@ -10336,7 +10323,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45958</v>
       </c>
@@ -10347,7 +10334,7 @@
         <v>14639</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45958</v>
       </c>
@@ -10358,7 +10345,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45958</v>
       </c>
@@ -10369,7 +10356,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45958</v>
       </c>
@@ -10380,7 +10367,7 @@
         <v>14802</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45958</v>
       </c>
@@ -10391,7 +10378,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45958</v>
       </c>
@@ -10402,7 +10389,7 @@
         <v>14850</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45958</v>
       </c>
@@ -10413,7 +10400,7 @@
         <v>14900</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45958</v>
       </c>
@@ -10424,7 +10411,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45958</v>
       </c>
@@ -10435,7 +10422,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45958</v>
       </c>
@@ -10446,7 +10433,7 @@
         <v>15425</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45958</v>
       </c>
@@ -10457,7 +10444,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45958</v>
       </c>
@@ -10468,7 +10455,7 @@
         <v>15400</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45958</v>
       </c>
@@ -10479,7 +10466,7 @@
         <v>15320</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45958</v>
       </c>
@@ -10490,7 +10477,7 @@
         <v>15108</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45958</v>
       </c>
@@ -10501,7 +10488,7 @@
         <v>15162</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45958</v>
       </c>
@@ -10512,7 +10499,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>45958</v>
       </c>
@@ -10523,7 +10510,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>45958</v>
       </c>
@@ -10534,7 +10521,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>45958</v>
       </c>
@@ -10545,7 +10532,7 @@
         <v>14933</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>45958</v>
       </c>
@@ -10556,7 +10543,7 @@
         <v>15135</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45958</v>
       </c>
@@ -10567,7 +10554,7 @@
         <v>15105</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45958</v>
       </c>
@@ -10578,7 +10565,7 @@
         <v>14980</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45958</v>
       </c>
@@ -10589,7 +10576,7 @@
         <v>15075</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>45958</v>
       </c>
@@ -10600,7 +10587,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>45958</v>
       </c>
@@ -10611,7 +10598,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>45958</v>
       </c>
@@ -10622,7 +10609,7 @@
         <v>15100</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>45958</v>
       </c>
@@ -10633,7 +10620,7 @@
         <v>15050</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>45958</v>
       </c>
@@ -10644,7 +10631,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>45958</v>
       </c>
@@ -10655,7 +10642,7 @@
         <v>15167</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>45958</v>
       </c>
@@ -10666,7 +10653,7 @@
         <v>14988</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>45958</v>
       </c>
@@ -10677,7 +10664,7 @@
         <v>14843</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>45958</v>
       </c>
@@ -10688,7 +10675,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>45958</v>
       </c>
@@ -10699,7 +10686,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>45958</v>
       </c>
@@ -10710,7 +10697,7 @@
         <v>14288</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>45958</v>
       </c>
@@ -10721,7 +10708,7 @@
         <v>14387</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>45958</v>
       </c>
@@ -10732,7 +10719,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>45958</v>
       </c>
@@ -10743,7 +10730,7 @@
         <v>14260</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>45958</v>
       </c>
@@ -10754,7 +10741,7 @@
         <v>14177</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>45958</v>
       </c>
@@ -10765,7 +10752,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>45958</v>
       </c>
@@ -10776,7 +10763,7 @@
         <v>14225</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>45958</v>
       </c>
@@ -10787,7 +10774,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>45958</v>
       </c>
@@ -10798,7 +10785,7 @@
         <v>14401</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>45958</v>
       </c>
@@ -10809,7 +10796,7 @@
         <v>14501</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>45958</v>
       </c>
@@ -10820,7 +10807,7 @@
         <v>14488</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>45958</v>
       </c>
@@ -10831,7 +10818,7 @@
         <v>14470</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>45958</v>
       </c>
@@ -10842,7 +10829,7 @@
         <v>14006</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>45958</v>
       </c>
@@ -10853,7 +10840,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>45958</v>
       </c>
@@ -10864,7 +10851,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>45958</v>
       </c>
@@ -10875,7 +10862,7 @@
         <v>13891</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>45958</v>
       </c>
@@ -10886,7 +10873,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B200" s="1">
         <v>45783</v>
       </c>
@@ -10894,7 +10881,7 @@
         <v>13316</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>45958</v>
       </c>
@@ -10905,7 +10892,7 @@
         <v>13130</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>45958</v>
       </c>
@@ -10916,7 +10903,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>45958</v>
       </c>
@@ -10927,7 +10914,7 @@
         <v>13150</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>45958</v>
       </c>
@@ -10938,7 +10925,7 @@
         <v>13422</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>45958</v>
       </c>
@@ -10949,7 +10936,7 @@
         <v>13373</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>45958</v>
       </c>
@@ -10960,7 +10947,7 @@
         <v>13211</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>45958</v>
       </c>
@@ -10971,7 +10958,7 @@
         <v>13256</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>45958</v>
       </c>
@@ -10982,7 +10969,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>45958</v>
       </c>
@@ -10993,7 +10980,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>45958</v>
       </c>
@@ -11004,7 +10991,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>45958</v>
       </c>
@@ -11015,7 +11002,7 @@
         <v>13361</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>45958</v>
       </c>
@@ -11026,7 +11013,7 @@
         <v>13125</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>45958</v>
       </c>
@@ -11037,7 +11024,7 @@
         <v>13180</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>45958</v>
       </c>
@@ -11048,7 +11035,7 @@
         <v>13315</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>45958</v>
       </c>
@@ -11059,7 +11046,7 @@
         <v>13331</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>45958</v>
       </c>
@@ -11070,7 +11057,7 @@
         <v>13386</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>45958</v>
       </c>
@@ -11081,7 +11068,7 @@
         <v>13385</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>45958</v>
       </c>
@@ -11092,7 +11079,7 @@
         <v>13343</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>45958</v>
       </c>
@@ -11103,7 +11090,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>45958</v>
       </c>
@@ -11114,7 +11101,7 @@
         <v>13145</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>45958</v>
       </c>
@@ -11125,7 +11112,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>45958</v>
       </c>
@@ -11136,7 +11123,7 @@
         <v>13360</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>45958</v>
       </c>
@@ -11147,7 +11134,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>45958</v>
       </c>
@@ -11158,7 +11145,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>45958</v>
       </c>
@@ -11169,7 +11156,7 @@
         <v>13615</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>45958</v>
       </c>
@@ -11180,7 +11167,7 @@
         <v>13677</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>45958</v>
       </c>
@@ -11191,7 +11178,7 @@
         <v>13655</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>45958</v>
       </c>
@@ -11202,7 +11189,7 @@
         <v>13730</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>45958</v>
       </c>
@@ -11213,7 +11200,7 @@
         <v>13415</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>45958</v>
       </c>
@@ -11224,7 +11211,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>45958</v>
       </c>
@@ -11235,7 +11222,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>45958</v>
       </c>
@@ -11246,7 +11233,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>45958</v>
       </c>
@@ -11257,7 +11244,7 @@
         <v>13575</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>45958</v>
       </c>
@@ -11268,7 +11255,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>45958</v>
       </c>
@@ -11279,7 +11266,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>45958</v>
       </c>
@@ -11290,7 +11277,7 @@
         <v>13850</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>45958</v>
       </c>
@@ -11301,7 +11288,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>45958</v>
       </c>
@@ -11312,7 +11299,7 @@
         <v>13975</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>45958</v>
       </c>
@@ -11323,7 +11310,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>45958</v>
       </c>
@@ -11334,7 +11321,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>45958</v>
       </c>
@@ -11345,7 +11332,7 @@
         <v>14200</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>45958</v>
       </c>
@@ -11356,7 +11343,7 @@
         <v>14245</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>45958</v>
       </c>
@@ -11367,7 +11354,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>45958</v>
       </c>
@@ -11378,7 +11365,7 @@
         <v>14350</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>45958</v>
       </c>
@@ -11389,7 +11376,7 @@
         <v>14360</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>45958</v>
       </c>
@@ -11400,7 +11387,7 @@
         <v>14555</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>45958</v>
       </c>
@@ -11411,7 +11398,7 @@
         <v>14576</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>45958</v>
       </c>
@@ -11422,7 +11409,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>45958</v>
       </c>
@@ -11433,7 +11420,7 @@
         <v>14666</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>45958</v>
       </c>
@@ -11444,7 +11431,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>45958</v>
       </c>
@@ -11455,7 +11442,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>45958</v>
       </c>
@@ -11466,7 +11453,7 @@
         <v>14494</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>45958</v>
       </c>
@@ -11477,7 +11464,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>45958</v>
       </c>
@@ -11488,7 +11475,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>45958</v>
       </c>
@@ -11499,7 +11486,7 @@
         <v>14635</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>45958</v>
       </c>
@@ -11510,7 +11497,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>45958</v>
       </c>
@@ -11521,7 +11508,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>45958</v>
       </c>
@@ -11532,7 +11519,7 @@
         <v>14689</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>45958</v>
       </c>
@@ -11543,7 +11530,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>45958</v>
       </c>
@@ -11554,7 +11541,7 @@
         <v>14530</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B261" s="1">
         <v>45877</v>
       </c>
@@ -11562,7 +11549,7 @@
         <v>14605</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>45958</v>
       </c>
@@ -11573,7 +11560,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>45958</v>
       </c>
@@ -11584,7 +11571,7 @@
         <v>14825</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>45958</v>
       </c>
@@ -11595,7 +11582,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>45958</v>
       </c>
@@ -11606,7 +11593,7 @@
         <v>14707</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>45958</v>
       </c>
@@ -11617,7 +11604,7 @@
         <v>14705</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>45958</v>
       </c>
@@ -11628,7 +11615,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>45958</v>
       </c>
@@ -11639,7 +11626,7 @@
         <v>14642</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>45958</v>
       </c>
@@ -11650,7 +11637,7 @@
         <v>14580</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>45958</v>
       </c>
@@ -11661,7 +11648,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>45958</v>
       </c>
@@ -11672,7 +11659,7 @@
         <v>14699</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>45958</v>
       </c>
@@ -11683,7 +11670,7 @@
         <v>14570</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45958</v>
       </c>
@@ -11694,7 +11681,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45958</v>
       </c>
@@ -11705,7 +11692,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45958</v>
       </c>
@@ -11716,7 +11703,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45958</v>
       </c>
@@ -11727,7 +11714,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45958</v>
       </c>
@@ -11738,7 +11725,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>45958</v>
       </c>
@@ -11749,7 +11736,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>45958</v>
       </c>
@@ -11760,7 +11747,7 @@
         <v>14665</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>45958</v>
       </c>
@@ -11771,7 +11758,7 @@
         <v>14601</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>45958</v>
       </c>
@@ -11782,7 +11769,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45958</v>
       </c>
@@ -11793,7 +11780,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>45958</v>
       </c>
@@ -11804,7 +11791,7 @@
         <v>14540</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>45958</v>
       </c>
@@ -11815,7 +11802,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>45958</v>
       </c>
@@ -11826,7 +11813,7 @@
         <v>14528</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>45958</v>
       </c>
@@ -11837,7 +11824,7 @@
         <v>14590</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>45958</v>
       </c>
@@ -11848,7 +11835,7 @@
         <v>14710</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>45958</v>
       </c>
@@ -11859,7 +11846,7 @@
         <v>14623</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>45958</v>
       </c>
@@ -11870,7 +11857,7 @@
         <v>14661</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>45958</v>
       </c>
@@ -11881,7 +11868,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>45958</v>
       </c>
@@ -11892,7 +11879,7 @@
         <v>14475</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>45958</v>
       </c>
@@ -11903,7 +11890,7 @@
         <v>14498</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>45958</v>
       </c>
@@ -11914,7 +11901,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>45958</v>
       </c>
@@ -11925,7 +11912,7 @@
         <v>14678</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>45958</v>
       </c>
@@ -11936,7 +11923,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>45958</v>
       </c>
@@ -11947,7 +11934,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>45958</v>
       </c>
@@ -11958,7 +11945,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>45958</v>
       </c>
@@ -11969,7 +11956,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>45958</v>
       </c>
@@ -11980,7 +11967,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>45958</v>
       </c>
@@ -11991,7 +11978,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>45958</v>
       </c>
@@ -12002,7 +11989,7 @@
         <v>14751</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>45958</v>
       </c>
@@ -12013,7 +12000,7 @@
         <v>14901</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>45958</v>
       </c>
@@ -12024,7 +12011,7 @@
         <v>14999</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>45958</v>
       </c>
@@ -12035,7 +12022,7 @@
         <v>14942</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>45958</v>
       </c>
@@ -12046,7 +12033,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>45958</v>
       </c>
@@ -12057,7 +12044,7 @@
         <v>14603</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>45958</v>
       </c>
@@ -12068,7 +12055,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>45958</v>
       </c>
@@ -12079,7 +12066,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>45958</v>
       </c>
@@ -12090,7 +12077,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>45958</v>
       </c>
@@ -12101,7 +12088,7 @@
         <v>14611</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>45958</v>
       </c>
@@ -12112,7 +12099,7 @@
         <v>14711</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>45958</v>
       </c>
@@ -12123,7 +12110,7 @@
         <v>14556</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>45958</v>
       </c>
@@ -12134,7 +12121,7 @@
         <v>15526</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>45958</v>
       </c>
@@ -12145,7 +12132,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>45958</v>
       </c>
@@ -12156,7 +12143,7 @@
         <v>14475</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>45959</v>
       </c>
@@ -12167,7 +12154,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>45960</v>
       </c>
@@ -12178,7 +12165,7 @@
         <v>14188</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>45960</v>
       </c>
@@ -12189,7 +12176,7 @@
         <v>14123</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>45964</v>
       </c>
@@ -12200,7 +12187,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>45966</v>
       </c>
@@ -12211,7 +12198,7 @@
         <v>13833</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>45967</v>
       </c>
@@ -12222,7 +12209,7 @@
         <v>13828</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>45971</v>
       </c>
@@ -12233,7 +12220,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>45972</v>
       </c>
@@ -12244,7 +12231,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>45974</v>
       </c>
@@ -12255,7 +12242,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>45975</v>
       </c>
@@ -12266,7 +12253,7 @@
         <v>13775</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>45978</v>
       </c>
@@ -12277,7 +12264,7 @@
         <v>13870</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>45979</v>
       </c>
@@ -12288,7 +12275,7 @@
         <v>14007</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>45980</v>
       </c>
@@ -12299,7 +12286,7 @@
         <v>14135</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>45981</v>
       </c>
@@ -12310,7 +12297,7 @@
         <v>14066</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>45982</v>
       </c>
@@ -12321,7 +12308,7 @@
         <v>14025</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>45985</v>
       </c>
@@ -12332,7 +12319,7 @@
         <v>14025</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>45986</v>
       </c>
@@ -12343,7 +12330,7 @@
         <v>13990</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>45987</v>
       </c>
@@ -12354,7 +12341,7 @@
         <v>14030</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>45988</v>
       </c>
@@ -12365,7 +12352,7 @@
         <v>14200</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>45992</v>
       </c>
@@ -12376,7 +12363,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>45993</v>
       </c>
@@ -12387,7 +12374,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>45995</v>
       </c>
@@ -12398,7 +12385,7 @@
         <v>14425</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>45995</v>
       </c>
@@ -12409,7 +12396,7 @@
         <v>14315</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>45996</v>
       </c>

--- a/src/results/(Terstruktur)Data Scrapping.xlsx
+++ b/src/results/(Terstruktur)Data Scrapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\PEI\Dashboard-Pertamina-VeloCT\src\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pekerjaan\Dashboard-Pertamina-VeloCT\src\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F71413-6B69-4C1F-9003-C492BE1928B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B81E6D4-46D5-4536-968B-63C97EAFA0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(Data)Biodesel" sheetId="1" r:id="rId1"/>
@@ -1159,8 +1159,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1237,11 +1237,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1555,9 +1555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C144"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>10143</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>8794</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>8939</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>9100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>9343</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>9112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>8954</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>8922</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>8770</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>7829</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>7494</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>6478</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>9456</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>9101</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>9271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>9081</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>8189</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>7680</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>6686</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>6890</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>7039</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>6626</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>6954</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>7112</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>7687</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>8026</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>8891</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>8737</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>8402</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>7835</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>8483</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>9028</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>8262</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>8779</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>75</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>9362</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>9493</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>9358</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>8815</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>8230</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>8302</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>8131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>7965</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>8518</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>8490</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>97</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>8491</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>101</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>7962</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>103</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>8161</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>8356</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>8261</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>8140</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>111</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>7949</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>7294</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>7341</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>119</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>7227</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>121</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>6371</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>125</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>7015</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>7403</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>129</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>7387</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>7348</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>6977</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>135</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>6970</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>137</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>139</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>7358</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>7157</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>147</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>8706</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>149</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>9539</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>8933</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>8019</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>8352</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>157</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>6941</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>159</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>7321</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>7887</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>163</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>9003</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>9265</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9329</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>9505</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>171</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>9457</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>173</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>9579</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>9434</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>177</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>10131</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>179</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>10229</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>11034</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>9852</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>10635</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>11930</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>189</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>12022</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>191</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>12854</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>193</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>13746</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>195</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>13177</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>197</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>13867</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>14436</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>201</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>15559</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>203</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>15211</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>205</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>13033</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>207</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>11070</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>209</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>8047</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>211</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>10281</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>213</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>10787</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>11012</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>217</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>12039</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>219</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>11520</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>221</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>11233</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>223</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>11473</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>12262</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>11493</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>229</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>10235</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>231</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>9998</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>233</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>10620</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>235</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>10687</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>237</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>10670</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>10653</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>241</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>10974</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>243</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>10896</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>245</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>11371</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>247</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>11517</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>12178</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>251</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>12453</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>11732</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>255</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>12161</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>257</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>12382</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>259</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>12389</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>261</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>12633</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>263</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>13384</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>265</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>14389</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>14615</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>269</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>13231</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>13929</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>273</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>14290</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>275</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>13742</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>277</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>12890</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>279</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>12874</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>281</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>13527</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>283</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>13948</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>285</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>14036</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>287</v>
       </c>
@@ -3149,13 +3149,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>265</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>267</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>269</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>271</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>273</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>275</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>277</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>279</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>291</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>283</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>285</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>287</v>
       </c>
@@ -3346,9 +3346,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D83"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>292</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2019</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2019</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2019</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2019</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2019</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2019</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2019</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2019</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2020</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2020</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2020</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2020</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2020</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2020</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2020</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2020</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2020</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2020</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2020</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2021</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2021</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2021</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2021</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2021</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2021</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2021</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2021</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2021</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2021</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2022</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2022</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2022</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2022</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2022</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2022</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2022</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2022</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2023</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2023</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2023</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2023</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2023</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2023</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2023</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2023</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2023</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2023</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2023</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2023</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2024</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2024</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2024</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2024</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2024</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2024</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2024</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2024</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2024</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2024</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2024</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2024</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2025</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2025</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2025</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2025</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2025</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2025</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2025</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2025</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2025</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2025</v>
       </c>
@@ -4512,9 +4512,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>293</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>300</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>302</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>304</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>47.92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>306</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>50.79</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>308</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>50.06</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>310</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>312</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>314</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>48.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>316</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>48.84</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>318</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>50.92</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>47.64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>298</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>50.38</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>300</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>50.01</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>304</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>50.62</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>306</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>50.32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>308</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>310</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>51.24</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>312</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>49.94</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>316</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>318</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>296</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>49.76</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>298</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>300</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>51.71</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>302</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>304</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>306</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>53.34</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>308</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>310</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>51.76</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>312</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>53.05</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>314</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>316</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>318</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>51.65</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>296</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>298</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>51.44</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>300</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>51.75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>302</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>304</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>52.54</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>306</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>52.92</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>308</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>52.68</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>310</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>312</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>314</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>316</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>52.33</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>318</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>53.01</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>296</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>51.36</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>298</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>52.02</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>300</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>302</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>52.61</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>304</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>53.23</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>306</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>53.51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>308</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>53.47</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>310</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>53.16</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>312</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>314</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>316</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>53.19</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>318</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>296</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>47.69</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>298</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>300</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>47.63</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>302</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>48.26</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>304</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>306</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>49.34</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>308</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>49.54</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>310</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>49.53</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>312</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>50.15</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>314</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>49.18</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>316</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>49.89</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>318</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>296</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>50.43</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>298</v>
       </c>
@@ -6850,7 +6850,7 @@
         <v>51.74</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>300</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>302</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>304</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>306</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>52.86</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>308</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>52.47</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>310</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>52.14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>312</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>52.76</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>314</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>51.67</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>316</v>
       </c>
@@ -7138,7 +7138,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>318</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>52.94</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>296</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>52.69</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>298</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>53.79</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>300</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>53.02</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>302</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>53.36</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>304</v>
       </c>
@@ -7330,7 +7330,7 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>306</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>54.79</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>308</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>54.42</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>310</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>54.16</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>312</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>54.83</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>314</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>53.72</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>316</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>318</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>54.92</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>296</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>54.54</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>298</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>55.95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>300</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>302</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>304</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>56.58</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>306</v>
       </c>
@@ -7746,7 +7746,7 @@
         <v>57.11</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>308</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>56.68</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>310</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>56.31</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>312</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>56.97</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>314</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>55.84</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>316</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>56.61</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>318</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>57.23</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>296</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>56.38</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>298</v>
       </c>
@@ -8002,7 +8002,7 @@
         <v>57.81</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>300</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>57.07</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>302</v>
       </c>
@@ -8066,7 +8066,7 @@
         <v>56.86</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>304</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>57.24</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>306</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>57.89</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>308</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>57.48</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>310</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>56.77</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>312</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>57.38</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>314</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>56.28</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>316</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>318</v>
       </c>
@@ -8322,7 +8322,7 @@
         <v>58.28</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>296</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>56.88</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>298</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>57.79</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>300</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>57.49</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>302</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>57.88</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>304</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>58.54</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>306</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>59.18</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -8546,7 +8546,7 @@
         <v>58.65</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>310</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>58.25</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>312</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>59.04</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>314</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>57.92</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>316</v>
       </c>
@@ -8682,9 +8682,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C339"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>373</v>
       </c>
@@ -8695,7 +8699,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45958</v>
       </c>
@@ -8706,7 +8710,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45958</v>
       </c>
@@ -8717,7 +8721,7 @@
         <v>13185</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45958</v>
       </c>
@@ -8728,7 +8732,7 @@
         <v>13170</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45958</v>
       </c>
@@ -8739,7 +8743,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45958</v>
       </c>
@@ -8750,7 +8754,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45958</v>
       </c>
@@ -8761,7 +8765,7 @@
         <v>13175</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45958</v>
       </c>
@@ -8772,7 +8776,7 @@
         <v>12888</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45958</v>
       </c>
@@ -8783,7 +8787,7 @@
         <v>12638</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45958</v>
       </c>
@@ -8794,7 +8798,7 @@
         <v>12718</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45958</v>
       </c>
@@ -8805,7 +8809,7 @@
         <v>12729</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45958</v>
       </c>
@@ -8816,7 +8820,7 @@
         <v>12640</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45958</v>
       </c>
@@ -8827,7 +8831,7 @@
         <v>12723</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45958</v>
       </c>
@@ -8838,7 +8842,7 @@
         <v>12738</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45958</v>
       </c>
@@ -8849,7 +8853,7 @@
         <v>12740</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45958</v>
       </c>
@@ -8860,7 +8864,7 @@
         <v>12725</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45958</v>
       </c>
@@ -8871,7 +8875,7 @@
         <v>12810</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45958</v>
       </c>
@@ -8882,7 +8886,7 @@
         <v>12804</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45958</v>
       </c>
@@ -8893,7 +8897,7 @@
         <v>12757</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45958</v>
       </c>
@@ -8904,7 +8908,7 @@
         <v>12775</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45958</v>
       </c>
@@ -8915,7 +8919,7 @@
         <v>12965</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45958</v>
       </c>
@@ -8926,7 +8930,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45958</v>
       </c>
@@ -8937,7 +8941,7 @@
         <v>13050</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45958</v>
       </c>
@@ -8948,7 +8952,7 @@
         <v>13036</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45958</v>
       </c>
@@ -8959,7 +8963,7 @@
         <v>13040</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45958</v>
       </c>
@@ -8970,7 +8974,7 @@
         <v>13105</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45958</v>
       </c>
@@ -8981,7 +8985,7 @@
         <v>13209</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45958</v>
       </c>
@@ -8992,7 +8996,7 @@
         <v>13119</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45958</v>
       </c>
@@ -9003,7 +9007,7 @@
         <v>13054</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45958</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>12939</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45958</v>
       </c>
@@ -9025,7 +9029,7 @@
         <v>12918</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45958</v>
       </c>
@@ -9036,7 +9040,7 @@
         <v>12830</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45958</v>
       </c>
@@ -9047,7 +9051,7 @@
         <v>12782</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45958</v>
       </c>
@@ -9058,7 +9062,7 @@
         <v>12677</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45958</v>
       </c>
@@ -9069,7 +9073,7 @@
         <v>12520</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45958</v>
       </c>
@@ -9080,7 +9084,7 @@
         <v>12588</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45958</v>
       </c>
@@ -9091,7 +9095,7 @@
         <v>12625</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>45958</v>
       </c>
@@ -9102,7 +9106,7 @@
         <v>12675</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>45958</v>
       </c>
@@ -9113,7 +9117,7 @@
         <v>12745</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>45958</v>
       </c>
@@ -9124,7 +9128,7 @@
         <v>12868</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>45958</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>12959</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>45958</v>
       </c>
@@ -9146,7 +9150,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>45958</v>
       </c>
@@ -9157,7 +9161,7 @@
         <v>13233</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>45958</v>
       </c>
@@ -9168,7 +9172,7 @@
         <v>13235</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>45958</v>
       </c>
@@ -9179,7 +9183,7 @@
         <v>13155</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45958</v>
       </c>
@@ -9190,7 +9194,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45958</v>
       </c>
@@ -9201,7 +9205,7 @@
         <v>13242</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>45958</v>
       </c>
@@ -9212,7 +9216,7 @@
         <v>13342</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>45958</v>
       </c>
@@ -9223,7 +9227,7 @@
         <v>13212</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>45958</v>
       </c>
@@ -9234,7 +9238,7 @@
         <v>13131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>45958</v>
       </c>
@@ -9245,7 +9249,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>45958</v>
       </c>
@@ -9256,7 +9260,7 @@
         <v>13058</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>45958</v>
       </c>
@@ -9267,7 +9271,7 @@
         <v>13089</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>45958</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>13118</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>45958</v>
       </c>
@@ -9289,7 +9293,7 @@
         <v>13070</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>45958</v>
       </c>
@@ -9300,7 +9304,7 @@
         <v>13035</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>45958</v>
       </c>
@@ -9311,7 +9315,7 @@
         <v>12925</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>45958</v>
       </c>
@@ -9322,7 +9326,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>45958</v>
       </c>
@@ -9333,7 +9337,7 @@
         <v>13358</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>45958</v>
       </c>
@@ -9344,7 +9348,7 @@
         <v>13407</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>45958</v>
       </c>
@@ -9355,7 +9359,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>45958</v>
       </c>
@@ -9366,7 +9370,7 @@
         <v>13570</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>45958</v>
       </c>
@@ -9377,7 +9381,7 @@
         <v>13759</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>45958</v>
       </c>
@@ -9388,7 +9392,7 @@
         <v>13928</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>45958</v>
       </c>
@@ -9399,7 +9403,7 @@
         <v>14004</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>45958</v>
       </c>
@@ -9410,7 +9414,7 @@
         <v>13978</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>45958</v>
       </c>
@@ -9421,7 +9425,7 @@
         <v>14106</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>45958</v>
       </c>
@@ -9432,7 +9436,7 @@
         <v>14027</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>45958</v>
       </c>
@@ -9443,7 +9447,7 @@
         <v>14138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>45958</v>
       </c>
@@ -9454,7 +9458,7 @@
         <v>14322</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>45958</v>
       </c>
@@ -9465,7 +9469,7 @@
         <v>14242</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>45958</v>
       </c>
@@ -9476,7 +9480,7 @@
         <v>14040</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>45958</v>
       </c>
@@ -9487,7 +9491,7 @@
         <v>14078</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>45958</v>
       </c>
@@ -9498,7 +9502,7 @@
         <v>14029</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>45958</v>
       </c>
@@ -9509,7 +9513,7 @@
         <v>14262</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>45958</v>
       </c>
@@ -9520,7 +9524,7 @@
         <v>14135</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>45958</v>
       </c>
@@ -9531,7 +9535,7 @@
         <v>13977</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>45958</v>
       </c>
@@ -9542,7 +9546,7 @@
         <v>14111</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>45958</v>
       </c>
@@ -9553,7 +9557,7 @@
         <v>14038</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>45958</v>
       </c>
@@ -9564,7 +9568,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>45958</v>
       </c>
@@ -9575,7 +9579,7 @@
         <v>14020</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>45958</v>
       </c>
@@ -9586,7 +9590,7 @@
         <v>14183</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>45958</v>
       </c>
@@ -9597,7 +9601,7 @@
         <v>14337</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>45958</v>
       </c>
@@ -9608,7 +9612,7 @@
         <v>14507</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>45958</v>
       </c>
@@ -9619,7 +9623,7 @@
         <v>14721</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>45958</v>
       </c>
@@ -9630,7 +9634,7 @@
         <v>14685</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>45958</v>
       </c>
@@ -9641,7 +9645,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>45958</v>
       </c>
@@ -9652,7 +9656,7 @@
         <v>14810</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>45958</v>
       </c>
@@ -9663,7 +9667,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>45958</v>
       </c>
@@ -9674,7 +9678,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>45958</v>
       </c>
@@ -9685,7 +9689,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45958</v>
       </c>
@@ -9696,7 +9700,7 @@
         <v>15310</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45958</v>
       </c>
@@ -9707,7 +9711,7 @@
         <v>15330</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>45958</v>
       </c>
@@ -9718,7 +9722,7 @@
         <v>15430</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>45958</v>
       </c>
@@ -9729,7 +9733,7 @@
         <v>15544</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>45958</v>
       </c>
@@ -9740,7 +9744,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>45958</v>
       </c>
@@ -9751,7 +9755,7 @@
         <v>15738</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>45958</v>
       </c>
@@ -9762,7 +9766,7 @@
         <v>15367</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>45958</v>
       </c>
@@ -9773,7 +9777,7 @@
         <v>15254</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>45958</v>
       </c>
@@ -9784,7 +9788,7 @@
         <v>15350</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>45958</v>
       </c>
@@ -9795,7 +9799,7 @@
         <v>15255</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>45958</v>
       </c>
@@ -9806,7 +9810,7 @@
         <v>15365</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>45958</v>
       </c>
@@ -9817,7 +9821,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>45958</v>
       </c>
@@ -9828,7 +9832,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>45958</v>
       </c>
@@ -9839,7 +9843,7 @@
         <v>14813</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>45958</v>
       </c>
@@ -9850,7 +9854,7 @@
         <v>14964</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>45958</v>
       </c>
@@ -9861,7 +9865,7 @@
         <v>15165</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>45958</v>
       </c>
@@ -9872,7 +9876,7 @@
         <v>15245</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>45958</v>
       </c>
@@ -9883,7 +9887,7 @@
         <v>15584</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>45958</v>
       </c>
@@ -9894,7 +9898,7 @@
         <v>15656</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>45958</v>
       </c>
@@ -9905,7 +9909,7 @@
         <v>15788</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>45958</v>
       </c>
@@ -9916,7 +9920,7 @@
         <v>15900</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>45958</v>
       </c>
@@ -9927,7 +9931,7 @@
         <v>15976</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>45958</v>
       </c>
@@ -9938,7 +9942,7 @@
         <v>16000</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>45958</v>
       </c>
@@ -9949,7 +9953,7 @@
         <v>15940</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>45958</v>
       </c>
@@ -9960,7 +9964,7 @@
         <v>15760</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>45958</v>
       </c>
@@ -9971,7 +9975,7 @@
         <v>15675</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>45958</v>
       </c>
@@ -9982,7 +9986,7 @@
         <v>15602</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>45958</v>
       </c>
@@ -9993,7 +9997,7 @@
         <v>15553</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>45958</v>
       </c>
@@ -10004,7 +10008,7 @@
         <v>15589</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>45958</v>
       </c>
@@ -10015,7 +10019,7 @@
         <v>15327</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>45958</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>14919</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>45958</v>
       </c>
@@ -10037,7 +10041,7 @@
         <v>14646</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>45958</v>
       </c>
@@ -10048,7 +10052,7 @@
         <v>14684</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>45958</v>
       </c>
@@ -10059,7 +10063,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>45958</v>
       </c>
@@ -10070,7 +10074,7 @@
         <v>14858</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>45958</v>
       </c>
@@ -10081,7 +10085,7 @@
         <v>14454</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>45958</v>
       </c>
@@ -10092,7 +10096,7 @@
         <v>14253</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>45958</v>
       </c>
@@ -10103,7 +10107,7 @@
         <v>14157</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>45958</v>
       </c>
@@ -10114,7 +10118,7 @@
         <v>14069</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>45958</v>
       </c>
@@ -10125,7 +10129,7 @@
         <v>13852</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>45958</v>
       </c>
@@ -10136,7 +10140,7 @@
         <v>13895</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>45958</v>
       </c>
@@ -10147,7 +10151,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>45958</v>
       </c>
@@ -10158,7 +10162,7 @@
         <v>14188</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>45958</v>
       </c>
@@ -10169,7 +10173,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>45958</v>
       </c>
@@ -10180,7 +10184,7 @@
         <v>13712</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>45958</v>
       </c>
@@ -10191,7 +10195,7 @@
         <v>13585</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>45958</v>
       </c>
@@ -10202,7 +10206,7 @@
         <v>13725</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>45958</v>
       </c>
@@ -10213,7 +10217,7 @@
         <v>13816</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>45958</v>
       </c>
@@ -10224,7 +10228,7 @@
         <v>13670</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>45958</v>
       </c>
@@ -10235,7 +10239,7 @@
         <v>13533</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>45958</v>
       </c>
@@ -10246,7 +10250,7 @@
         <v>13605</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>45958</v>
       </c>
@@ -10257,7 +10261,7 @@
         <v>13750</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>45958</v>
       </c>
@@ -10268,7 +10272,7 @@
         <v>13889</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>45958</v>
       </c>
@@ -10279,7 +10283,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>45958</v>
       </c>
@@ -10290,7 +10294,7 @@
         <v>14008</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>45958</v>
       </c>
@@ -10301,7 +10305,7 @@
         <v>14150</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>45958</v>
       </c>
@@ -10312,7 +10316,7 @@
         <v>14265</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>45958</v>
       </c>
@@ -10323,7 +10327,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>45958</v>
       </c>
@@ -10334,7 +10338,7 @@
         <v>14639</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>45958</v>
       </c>
@@ -10345,7 +10349,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>45958</v>
       </c>
@@ -10356,7 +10360,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>45958</v>
       </c>
@@ -10367,7 +10371,7 @@
         <v>14802</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>45958</v>
       </c>
@@ -10378,7 +10382,7 @@
         <v>14888</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>45958</v>
       </c>
@@ -10389,7 +10393,7 @@
         <v>14850</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>45958</v>
       </c>
@@ -10400,7 +10404,7 @@
         <v>14900</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>45958</v>
       </c>
@@ -10411,7 +10415,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>45958</v>
       </c>
@@ -10422,7 +10426,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>45958</v>
       </c>
@@ -10433,7 +10437,7 @@
         <v>15425</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>45958</v>
       </c>
@@ -10444,7 +10448,7 @@
         <v>15275</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>45958</v>
       </c>
@@ -10455,7 +10459,7 @@
         <v>15400</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>45958</v>
       </c>
@@ -10466,7 +10470,7 @@
         <v>15320</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>45958</v>
       </c>
@@ -10477,7 +10481,7 @@
         <v>15108</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>45958</v>
       </c>
@@ -10488,7 +10492,7 @@
         <v>15162</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>45958</v>
       </c>
@@ -10499,7 +10503,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>45958</v>
       </c>
@@ -10510,7 +10514,7 @@
         <v>14740</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>45958</v>
       </c>
@@ -10521,7 +10525,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>45958</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>14933</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>45958</v>
       </c>
@@ -10543,7 +10547,7 @@
         <v>15135</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>45958</v>
       </c>
@@ -10554,7 +10558,7 @@
         <v>15105</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>45958</v>
       </c>
@@ -10565,7 +10569,7 @@
         <v>14980</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>45958</v>
       </c>
@@ -10576,7 +10580,7 @@
         <v>15075</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>45958</v>
       </c>
@@ -10587,7 +10591,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>45958</v>
       </c>
@@ -10598,7 +10602,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>45958</v>
       </c>
@@ -10609,7 +10613,7 @@
         <v>15100</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>45958</v>
       </c>
@@ -10620,7 +10624,7 @@
         <v>15050</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>45958</v>
       </c>
@@ -10631,7 +10635,7 @@
         <v>15118</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>45958</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>15167</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>45958</v>
       </c>
@@ -10653,7 +10657,7 @@
         <v>14988</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>45958</v>
       </c>
@@ -10664,7 +10668,7 @@
         <v>14843</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>45958</v>
       </c>
@@ -10675,7 +10679,7 @@
         <v>14781</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>45958</v>
       </c>
@@ -10686,7 +10690,7 @@
         <v>14800</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>45958</v>
       </c>
@@ -10697,7 +10701,7 @@
         <v>14288</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>45958</v>
       </c>
@@ -10708,7 +10712,7 @@
         <v>14387</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>45958</v>
       </c>
@@ -10719,7 +10723,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>45958</v>
       </c>
@@ -10730,7 +10734,7 @@
         <v>14260</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>45958</v>
       </c>
@@ -10741,7 +10745,7 @@
         <v>14177</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>45958</v>
       </c>
@@ -10752,7 +10756,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>45958</v>
       </c>
@@ -10763,7 +10767,7 @@
         <v>14225</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>45958</v>
       </c>
@@ -10774,7 +10778,7 @@
         <v>14001</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>45958</v>
       </c>
@@ -10785,7 +10789,7 @@
         <v>14401</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>45958</v>
       </c>
@@ -10796,7 +10800,7 @@
         <v>14501</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>45958</v>
       </c>
@@ -10807,7 +10811,7 @@
         <v>14488</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>45958</v>
       </c>
@@ -10818,7 +10822,7 @@
         <v>14470</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>45958</v>
       </c>
@@ -10829,7 +10833,7 @@
         <v>14006</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>45958</v>
       </c>
@@ -10840,7 +10844,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>45958</v>
       </c>
@@ -10851,7 +10855,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>45958</v>
       </c>
@@ -10862,7 +10866,7 @@
         <v>13891</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>45958</v>
       </c>
@@ -10873,7 +10877,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B200" s="1">
         <v>45783</v>
       </c>
@@ -10881,7 +10885,7 @@
         <v>13316</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>45958</v>
       </c>
@@ -10892,7 +10896,7 @@
         <v>13130</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>45958</v>
       </c>
@@ -10903,7 +10907,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>45958</v>
       </c>
@@ -10914,7 +10918,7 @@
         <v>13150</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>45958</v>
       </c>
@@ -10925,7 +10929,7 @@
         <v>13422</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>45958</v>
       </c>
@@ -10936,7 +10940,7 @@
         <v>13373</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>45958</v>
       </c>
@@ -10947,7 +10951,7 @@
         <v>13211</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>45958</v>
       </c>
@@ -10958,7 +10962,7 @@
         <v>13256</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>45958</v>
       </c>
@@ -10969,7 +10973,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>45958</v>
       </c>
@@ -10980,7 +10984,7 @@
         <v>13400</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>45958</v>
       </c>
@@ -10991,7 +10995,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>45958</v>
       </c>
@@ -11002,7 +11006,7 @@
         <v>13361</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>45958</v>
       </c>
@@ -11013,7 +11017,7 @@
         <v>13125</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>45958</v>
       </c>
@@ -11024,7 +11028,7 @@
         <v>13180</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>45958</v>
       </c>
@@ -11035,7 +11039,7 @@
         <v>13315</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>45958</v>
       </c>
@@ -11046,7 +11050,7 @@
         <v>13331</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>45958</v>
       </c>
@@ -11057,7 +11061,7 @@
         <v>13386</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>45958</v>
       </c>
@@ -11068,7 +11072,7 @@
         <v>13385</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>45958</v>
       </c>
@@ -11079,7 +11083,7 @@
         <v>13343</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>45958</v>
       </c>
@@ -11090,7 +11094,7 @@
         <v>13328</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>45958</v>
       </c>
@@ -11101,7 +11105,7 @@
         <v>13145</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>45958</v>
       </c>
@@ -11112,7 +11116,7 @@
         <v>13225</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>45958</v>
       </c>
@@ -11123,7 +11127,7 @@
         <v>13360</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>45958</v>
       </c>
@@ -11134,7 +11138,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>45958</v>
       </c>
@@ -11145,7 +11149,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>45958</v>
       </c>
@@ -11156,7 +11160,7 @@
         <v>13615</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>45958</v>
       </c>
@@ -11167,7 +11171,7 @@
         <v>13677</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>45958</v>
       </c>
@@ -11178,7 +11182,7 @@
         <v>13655</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>45958</v>
       </c>
@@ -11189,7 +11193,7 @@
         <v>13730</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>45958</v>
       </c>
@@ -11200,7 +11204,7 @@
         <v>13415</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>45958</v>
       </c>
@@ -11211,7 +11215,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>45958</v>
       </c>
@@ -11222,7 +11226,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>45958</v>
       </c>
@@ -11233,7 +11237,7 @@
         <v>13550</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>45958</v>
       </c>
@@ -11244,7 +11248,7 @@
         <v>13575</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>45958</v>
       </c>
@@ -11255,7 +11259,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>45958</v>
       </c>
@@ -11266,7 +11270,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>45958</v>
       </c>
@@ -11277,7 +11281,7 @@
         <v>13850</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>45958</v>
       </c>
@@ -11288,7 +11292,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>45958</v>
       </c>
@@ -11299,7 +11303,7 @@
         <v>13975</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>45958</v>
       </c>
@@ -11310,7 +11314,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>45958</v>
       </c>
@@ -11321,7 +11325,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>45958</v>
       </c>
@@ -11332,7 +11336,7 @@
         <v>14200</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>45958</v>
       </c>
@@ -11343,7 +11347,7 @@
         <v>14245</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>45958</v>
       </c>
@@ -11354,7 +11358,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>45958</v>
       </c>
@@ -11365,7 +11369,7 @@
         <v>14350</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>45958</v>
       </c>
@@ -11376,7 +11380,7 @@
         <v>14360</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>45958</v>
       </c>
@@ -11387,7 +11391,7 @@
         <v>14555</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>45958</v>
       </c>
@@ -11398,7 +11402,7 @@
         <v>14576</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>45958</v>
       </c>
@@ -11409,7 +11413,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>45958</v>
       </c>
@@ -11420,7 +11424,7 @@
         <v>14666</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>45958</v>
       </c>
@@ -11431,7 +11435,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>45958</v>
       </c>
@@ -11442,7 +11446,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>45958</v>
       </c>
@@ -11453,7 +11457,7 @@
         <v>14494</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>45958</v>
       </c>
@@ -11464,7 +11468,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>45958</v>
       </c>
@@ -11475,7 +11479,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>45958</v>
       </c>
@@ -11486,7 +11490,7 @@
         <v>14635</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>45958</v>
       </c>
@@ -11497,7 +11501,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>45958</v>
       </c>
@@ -11508,7 +11512,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>45958</v>
       </c>
@@ -11519,7 +11523,7 @@
         <v>14689</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>45958</v>
       </c>
@@ -11530,7 +11534,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>45958</v>
       </c>
@@ -11541,7 +11545,7 @@
         <v>14530</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B261" s="1">
         <v>45877</v>
       </c>
@@ -11549,7 +11553,7 @@
         <v>14605</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>45958</v>
       </c>
@@ -11560,7 +11564,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>45958</v>
       </c>
@@ -11571,7 +11575,7 @@
         <v>14825</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>45958</v>
       </c>
@@ -11582,7 +11586,7 @@
         <v>14852</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>45958</v>
       </c>
@@ -11593,7 +11597,7 @@
         <v>14707</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>45958</v>
       </c>
@@ -11604,7 +11608,7 @@
         <v>14705</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>45958</v>
       </c>
@@ -11615,7 +11619,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>45958</v>
       </c>
@@ -11626,7 +11630,7 @@
         <v>14642</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>45958</v>
       </c>
@@ -11637,7 +11641,7 @@
         <v>14580</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>45958</v>
       </c>
@@ -11648,7 +11652,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>45958</v>
       </c>
@@ -11659,7 +11663,7 @@
         <v>14699</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>45958</v>
       </c>
@@ -11670,7 +11674,7 @@
         <v>14570</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>45958</v>
       </c>
@@ -11681,7 +11685,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>45958</v>
       </c>
@@ -11692,7 +11696,7 @@
         <v>14550</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>45958</v>
       </c>
@@ -11703,7 +11707,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>45958</v>
       </c>
@@ -11714,7 +11718,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>45958</v>
       </c>
@@ -11725,7 +11729,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>45958</v>
       </c>
@@ -11736,7 +11740,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>45958</v>
       </c>
@@ -11747,7 +11751,7 @@
         <v>14665</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>45958</v>
       </c>
@@ -11758,7 +11762,7 @@
         <v>14601</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>45958</v>
       </c>
@@ -11769,7 +11773,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>45958</v>
       </c>
@@ -11780,7 +11784,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>45958</v>
       </c>
@@ -11791,7 +11795,7 @@
         <v>14540</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>45958</v>
       </c>
@@ -11802,7 +11806,7 @@
         <v>14525</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>45958</v>
       </c>
@@ -11813,7 +11817,7 @@
         <v>14528</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>45958</v>
       </c>
@@ -11824,7 +11828,7 @@
         <v>14590</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>45958</v>
       </c>
@@ -11835,7 +11839,7 @@
         <v>14710</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>45958</v>
       </c>
@@ -11846,7 +11850,7 @@
         <v>14623</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>45958</v>
       </c>
@@ -11857,7 +11861,7 @@
         <v>14661</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>45958</v>
       </c>
@@ -11868,7 +11872,7 @@
         <v>14755</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>45958</v>
       </c>
@@ -11879,7 +11883,7 @@
         <v>14475</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>45958</v>
       </c>
@@ -11890,7 +11894,7 @@
         <v>14498</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>45958</v>
       </c>
@@ -11901,7 +11905,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>45958</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>14678</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>45958</v>
       </c>
@@ -11923,7 +11927,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>45958</v>
       </c>
@@ -11934,7 +11938,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>45958</v>
       </c>
@@ -11945,7 +11949,7 @@
         <v>14575</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>45958</v>
       </c>
@@ -11956,7 +11960,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>45958</v>
       </c>
@@ -11967,7 +11971,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>45958</v>
       </c>
@@ -11978,7 +11982,7 @@
         <v>14650</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>45958</v>
       </c>
@@ -11989,7 +11993,7 @@
         <v>14751</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>45958</v>
       </c>
@@ -12000,7 +12004,7 @@
         <v>14901</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>45958</v>
       </c>
@@ -12011,7 +12015,7 @@
         <v>14999</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>45958</v>
       </c>
@@ -12022,7 +12026,7 @@
         <v>14942</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>45958</v>
       </c>
@@ -12033,7 +12037,7 @@
         <v>14545</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>45958</v>
       </c>
@@ -12044,7 +12048,7 @@
         <v>14603</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>45958</v>
       </c>
@@ -12055,7 +12059,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>45958</v>
       </c>
@@ -12066,7 +12070,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>45958</v>
       </c>
@@ -12077,7 +12081,7 @@
         <v>14625</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>45958</v>
       </c>
@@ -12088,7 +12092,7 @@
         <v>14611</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>45958</v>
       </c>
@@ -12099,7 +12103,7 @@
         <v>14711</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>45958</v>
       </c>
@@ -12110,7 +12114,7 @@
         <v>14556</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>45958</v>
       </c>
@@ -12121,7 +12125,7 @@
         <v>15526</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>45958</v>
       </c>
@@ -12132,7 +12136,7 @@
         <v>14500</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>45958</v>
       </c>
@@ -12143,7 +12147,7 @@
         <v>14475</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>45959</v>
       </c>
@@ -12154,7 +12158,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>45960</v>
       </c>
@@ -12165,7 +12169,7 @@
         <v>14188</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>45960</v>
       </c>
@@ -12176,7 +12180,7 @@
         <v>14123</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>45964</v>
       </c>
@@ -12187,7 +12191,7 @@
         <v>13900</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>45966</v>
       </c>
@@ -12198,7 +12202,7 @@
         <v>13833</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>45967</v>
       </c>
@@ -12209,7 +12213,7 @@
         <v>13828</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>45971</v>
       </c>
@@ -12220,7 +12224,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>45972</v>
       </c>
@@ -12231,7 +12235,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>45974</v>
       </c>
@@ -12242,7 +12246,7 @@
         <v>13800</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>45975</v>
       </c>
@@ -12253,7 +12257,7 @@
         <v>13775</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>45978</v>
       </c>
@@ -12264,7 +12268,7 @@
         <v>13870</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>45979</v>
       </c>
@@ -12275,7 +12279,7 @@
         <v>14007</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>45980</v>
       </c>
@@ -12286,7 +12290,7 @@
         <v>14135</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>45981</v>
       </c>
@@ -12297,7 +12301,7 @@
         <v>14066</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>45982</v>
       </c>
@@ -12308,7 +12312,7 @@
         <v>14025</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>45985</v>
       </c>
@@ -12319,7 +12323,7 @@
         <v>14025</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>45986</v>
       </c>
@@ -12330,7 +12334,7 @@
         <v>13990</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>45987</v>
       </c>
@@ -12341,7 +12345,7 @@
         <v>14030</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>45988</v>
       </c>
@@ -12352,7 +12356,7 @@
         <v>14200</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>45992</v>
       </c>
@@ -12363,7 +12367,7 @@
         <v>14250</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>45993</v>
       </c>
@@ -12374,7 +12378,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>45995</v>
       </c>
@@ -12385,27 +12389,13 @@
         <v>14425</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" s="1">
-        <v>45995</v>
-      </c>
-      <c r="B338" s="1">
-        <v>45995</v>
-      </c>
-      <c r="C338">
-        <v>14315</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="1">
-        <v>45996</v>
-      </c>
-      <c r="B339" s="1">
-        <v>45996</v>
-      </c>
-      <c r="C339">
-        <v>14415</v>
-      </c>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
